--- a/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Old Spreadsheets/Connors Fish Tag Data 2024.xlsx
+++ b/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Old Spreadsheets/Connors Fish Tag Data 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Source Data\Tagging\Tag Returns\Tag Returns spreadsheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Old Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9A561D-6781-462B-96A3-A8C2553B8B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{AE9A561D-6781-462B-96A3-A8C2553B8B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7A99454-54B6-4908-9A87-38120F18D037}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19150" yWindow="0" windowWidth="19400" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5805" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5799" uniqueCount="1218">
   <si>
     <t>DATE</t>
   </si>
@@ -3578,9 +3578,6 @@
     <t>xxxs230823</t>
   </si>
   <si>
-    <t>0609123 (XX)</t>
-  </si>
-  <si>
     <t>070923 (XX)</t>
   </si>
   <si>
@@ -3629,9 +3626,6 @@
     <t>See coordinates</t>
   </si>
   <si>
-    <t>Frozen - Code unclear to determine date</t>
-  </si>
-  <si>
     <t>Used closest date, which was August 29th</t>
   </si>
   <si>
@@ -3690,6 +3684,15 @@
   </si>
   <si>
     <t>300823 - Comeaus</t>
+  </si>
+  <si>
+    <t>30-12-2023</t>
+  </si>
+  <si>
+    <t>07-12-2023</t>
+  </si>
+  <si>
+    <t>05-01-2024</t>
   </si>
 </sst>
 </file>
@@ -4075,7 +4078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4268,6 +4271,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4550,22 +4554,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26710EB7-6397-4E78-96F2-1050B80714FD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Q163"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="39" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="39" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="39" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="39" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" style="39" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="39" customWidth="1"/>
+    <col min="5" max="5" width="28.453125" style="39" customWidth="1"/>
     <col min="6" max="6" width="48" style="39" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="39" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" style="39" customWidth="1"/>
     <col min="8" max="8" width="23" style="39" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="39" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" style="39" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" style="39" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="22.1796875" style="39" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="28" style="39" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="63" t="s">
         <v>1002</v>
       </c>
@@ -4580,7 +4584,7 @@
       <c r="J1" s="64"/>
       <c r="K1" s="64"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
         <v>2</v>
       </c>
@@ -4615,7 +4619,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="39">
         <v>564179</v>
       </c>
@@ -4647,7 +4651,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="39">
         <v>567880</v>
       </c>
@@ -4676,7 +4680,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="39">
         <v>471737</v>
       </c>
@@ -4708,7 +4712,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="39">
         <v>567226</v>
       </c>
@@ -4737,7 +4741,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="39">
         <v>564204</v>
       </c>
@@ -4769,7 +4773,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="39">
         <v>564214</v>
       </c>
@@ -4798,7 +4802,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="39">
         <v>567067</v>
       </c>
@@ -4827,7 +4831,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="39">
         <v>474896</v>
       </c>
@@ -4856,7 +4860,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="39">
         <v>521924</v>
       </c>
@@ -4879,7 +4883,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="39">
         <v>569507</v>
       </c>
@@ -4908,15 +4912,15 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="39">
         <v>564107</v>
       </c>
       <c r="B13" s="62">
         <v>45510</v>
       </c>
-      <c r="C13" s="57">
-        <v>45875</v>
+      <c r="C13" s="57" t="s">
+        <v>1004</v>
       </c>
       <c r="D13" s="58" t="s">
         <v>947</v>
@@ -4940,15 +4944,15 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="39">
         <v>471754</v>
       </c>
       <c r="B14" s="62">
         <v>45538</v>
       </c>
-      <c r="C14" s="57">
-        <v>45903</v>
+      <c r="C14" s="57" t="s">
+        <v>1004</v>
       </c>
       <c r="D14" s="39" t="s">
         <v>1026</v>
@@ -4969,7 +4973,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="39">
         <v>567265</v>
       </c>
@@ -4998,7 +5002,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="39">
         <v>564161</v>
       </c>
@@ -5027,7 +5031,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="39">
         <v>564066</v>
       </c>
@@ -5062,7 +5066,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="39">
         <v>564434</v>
       </c>
@@ -5091,7 +5095,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="39">
         <v>577797</v>
       </c>
@@ -5120,7 +5124,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="39">
         <v>578873</v>
       </c>
@@ -5149,7 +5153,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="39">
         <v>564202</v>
       </c>
@@ -5178,7 +5182,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="39">
         <v>564961</v>
       </c>
@@ -5207,7 +5211,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="39">
         <v>577781</v>
       </c>
@@ -5215,7 +5219,7 @@
         <v>45561</v>
       </c>
       <c r="C23" s="57">
-        <v>45926</v>
+        <v>45561</v>
       </c>
       <c r="D23" s="39" t="s">
         <v>818</v>
@@ -5239,7 +5243,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="39">
         <v>567029</v>
       </c>
@@ -5271,7 +5275,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="39">
         <v>575814</v>
       </c>
@@ -5297,7 +5301,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="39">
         <v>569623</v>
       </c>
@@ -5323,7 +5327,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="39">
         <v>567881</v>
       </c>
@@ -5349,7 +5353,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="39">
         <v>567083</v>
       </c>
@@ -5372,7 +5376,7 @@
         <v>593</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K28" s="39" t="s">
         <v>742</v>
@@ -5381,7 +5385,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="39">
         <v>528137</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>593</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K29" s="39" t="s">
         <v>732</v>
@@ -5413,7 +5417,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="39">
         <v>567428</v>
       </c>
@@ -5436,7 +5440,7 @@
         <v>593</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K30" s="39" t="s">
         <v>732</v>
@@ -5445,7 +5449,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="39">
         <v>567482</v>
       </c>
@@ -5471,19 +5475,19 @@
         <v>84</v>
       </c>
       <c r="K31" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L31" t="s">
         <v>1065</v>
       </c>
       <c r="O31" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P31" t="s">
         <v>1193</v>
       </c>
-      <c r="P31" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="39">
         <v>569215</v>
       </c>
@@ -5509,19 +5513,19 @@
         <v>84</v>
       </c>
       <c r="K32" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L32" t="s">
         <v>1065</v>
       </c>
       <c r="O32" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P32" t="s">
         <v>1193</v>
       </c>
-      <c r="P32" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="39">
         <v>569032</v>
       </c>
@@ -5547,19 +5551,19 @@
         <v>84</v>
       </c>
       <c r="K33" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L33" t="s">
         <v>1065</v>
       </c>
       <c r="O33" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P33" t="s">
         <v>1193</v>
       </c>
-      <c r="P33" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="39">
         <v>471466</v>
       </c>
@@ -5585,22 +5589,22 @@
         <v>50</v>
       </c>
       <c r="K34" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L34" t="s">
         <v>1062</v>
       </c>
       <c r="O34" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="P34" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="Q34" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="39">
         <v>564145</v>
       </c>
@@ -5626,22 +5630,22 @@
         <v>50</v>
       </c>
       <c r="K35" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L35" t="s">
         <v>1062</v>
       </c>
       <c r="O35" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="P35" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="Q35" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="39">
         <v>564460</v>
       </c>
@@ -5667,19 +5671,19 @@
         <v>84</v>
       </c>
       <c r="K36" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L36" t="s">
         <v>1065</v>
       </c>
       <c r="O36" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P36" t="s">
         <v>1193</v>
       </c>
-      <c r="P36" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="39">
         <v>564341</v>
       </c>
@@ -5705,19 +5709,19 @@
         <v>84</v>
       </c>
       <c r="K37" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L37" t="s">
         <v>1065</v>
       </c>
       <c r="O37" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P37" t="s">
         <v>1193</v>
       </c>
-      <c r="P37" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="39">
         <v>564756</v>
       </c>
@@ -5743,19 +5747,19 @@
         <v>171</v>
       </c>
       <c r="K38" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L38" t="s">
         <v>1066</v>
       </c>
       <c r="O38" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="P38" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="39">
         <v>563807</v>
       </c>
@@ -5763,7 +5767,7 @@
         <v>45378</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>1196</v>
+        <v>1215</v>
       </c>
       <c r="D39" s="39" t="s">
         <v>817</v>
@@ -5772,7 +5776,7 @@
         <v>1067</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="I39" s="39" t="s">
         <v>593</v>
@@ -5781,7 +5785,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="39">
         <v>574694</v>
       </c>
@@ -5807,19 +5811,19 @@
         <v>108</v>
       </c>
       <c r="K40" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L40" t="s">
         <v>1069</v>
       </c>
       <c r="O40" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="P40" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="39">
         <v>577472</v>
       </c>
@@ -5845,27 +5849,27 @@
         <v>185</v>
       </c>
       <c r="K41" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L41" t="s">
         <v>1070</v>
       </c>
       <c r="O41" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="P41" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="39">
         <v>572457</v>
       </c>
       <c r="B42" s="62">
         <v>45372</v>
       </c>
-      <c r="C42" s="39" t="s">
-        <v>1202</v>
+      <c r="C42" s="74" t="s">
+        <v>1216</v>
       </c>
       <c r="D42" s="39" t="s">
         <v>794</v>
@@ -5880,7 +5884,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="39">
         <v>567442</v>
       </c>
@@ -5903,7 +5907,7 @@
         <v>593</v>
       </c>
       <c r="J43" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K43" s="39" t="s">
         <v>742</v>
@@ -5912,7 +5916,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="39">
         <v>564416</v>
       </c>
@@ -5935,7 +5939,7 @@
         <v>593</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K44" s="39" t="s">
         <v>742</v>
@@ -5944,7 +5948,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="39">
         <v>567465</v>
       </c>
@@ -5967,7 +5971,7 @@
         <v>593</v>
       </c>
       <c r="J45" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K45" s="39" t="s">
         <v>742</v>
@@ -5976,7 +5980,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="39">
         <v>564456</v>
       </c>
@@ -5999,7 +6003,7 @@
         <v>593</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K46" s="39" t="s">
         <v>742</v>
@@ -6008,7 +6012,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="39">
         <v>564640</v>
       </c>
@@ -6031,7 +6035,7 @@
         <v>593</v>
       </c>
       <c r="J47" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K47" s="39" t="s">
         <v>742</v>
@@ -6040,7 +6044,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="39">
         <v>567923</v>
       </c>
@@ -6063,7 +6067,7 @@
         <v>593</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K48" s="39" t="s">
         <v>742</v>
@@ -6072,7 +6076,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="39">
         <v>564713</v>
       </c>
@@ -6098,19 +6102,19 @@
         <v>50</v>
       </c>
       <c r="K49" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L49" t="s">
         <v>1062</v>
       </c>
       <c r="O49" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="P49" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="39">
         <v>564637</v>
       </c>
@@ -6136,19 +6140,19 @@
         <v>50</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L50" t="s">
         <v>1062</v>
       </c>
       <c r="O50" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="P50" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="39">
         <v>564334</v>
       </c>
@@ -6174,19 +6178,19 @@
         <v>50</v>
       </c>
       <c r="K51" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L51" t="s">
         <v>1062</v>
       </c>
       <c r="O51" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="P51" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="39">
         <v>564312</v>
       </c>
@@ -6212,19 +6216,19 @@
         <v>50</v>
       </c>
       <c r="K52" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L52" t="s">
         <v>1062</v>
       </c>
       <c r="O52" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="P52" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="39">
         <v>564349</v>
       </c>
@@ -6247,7 +6251,7 @@
         <v>593</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K53" s="39" t="s">
         <v>742</v>
@@ -6256,7 +6260,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="39">
         <v>564783</v>
       </c>
@@ -6282,13 +6286,13 @@
         <v>50</v>
       </c>
       <c r="K54" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L54" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="39">
         <v>564604</v>
       </c>
@@ -6314,13 +6318,13 @@
         <v>50</v>
       </c>
       <c r="K55" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L55" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="39">
         <v>564864</v>
       </c>
@@ -6346,13 +6350,13 @@
         <v>50</v>
       </c>
       <c r="K56" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L56" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="39">
         <v>564417</v>
       </c>
@@ -6378,13 +6382,13 @@
         <v>50</v>
       </c>
       <c r="K57" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L57" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="39">
         <v>564590</v>
       </c>
@@ -6392,7 +6396,7 @@
         <v>45366</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>1046</v>
+        <v>1217</v>
       </c>
       <c r="D58" s="39" t="s">
         <v>838</v>
@@ -6407,7 +6411,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="39">
         <v>564764</v>
       </c>
@@ -6433,13 +6437,13 @@
         <v>50</v>
       </c>
       <c r="K59" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L59" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="39">
         <v>564554</v>
       </c>
@@ -6465,13 +6469,13 @@
         <v>50</v>
       </c>
       <c r="K60" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L60" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="39">
         <v>564761</v>
       </c>
@@ -6497,13 +6501,13 @@
         <v>50</v>
       </c>
       <c r="K61" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L61" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="39">
         <v>564463</v>
       </c>
@@ -6529,13 +6533,13 @@
         <v>50</v>
       </c>
       <c r="K62" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L62" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="39">
         <v>473112</v>
       </c>
@@ -6552,7 +6556,7 @@
         <v>1052</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I63" s="39" t="s">
         <v>593</v>
@@ -6561,19 +6565,19 @@
         <v>69</v>
       </c>
       <c r="K63" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L63" t="s">
         <v>1092</v>
       </c>
       <c r="O63" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P63" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="39">
         <v>471616</v>
       </c>
@@ -6590,7 +6594,7 @@
         <v>1091</v>
       </c>
       <c r="H64" s="39" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I64" s="39" t="s">
         <v>593</v>
@@ -6599,19 +6603,19 @@
         <v>69</v>
       </c>
       <c r="K64" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L64" t="s">
         <v>1092</v>
       </c>
       <c r="O64" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P64" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="39">
         <v>564411</v>
       </c>
@@ -6628,7 +6632,7 @@
         <v>1052</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I65" s="39" t="s">
         <v>593</v>
@@ -6637,19 +6641,19 @@
         <v>69</v>
       </c>
       <c r="K65" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L65" t="s">
         <v>1092</v>
       </c>
       <c r="O65" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P65" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="39">
         <v>564358</v>
       </c>
@@ -6666,7 +6670,7 @@
         <v>1095</v>
       </c>
       <c r="H66" s="39" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I66" s="39" t="s">
         <v>593</v>
@@ -6675,19 +6679,19 @@
         <v>69</v>
       </c>
       <c r="K66" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L66" t="s">
         <v>1092</v>
       </c>
       <c r="O66" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P66" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="39">
         <v>532075</v>
       </c>
@@ -6704,7 +6708,7 @@
         <v>1087</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I67" s="39" t="s">
         <v>593</v>
@@ -6713,19 +6717,19 @@
         <v>69</v>
       </c>
       <c r="K67" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L67" t="s">
         <v>1092</v>
       </c>
       <c r="O67" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P67" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="39">
         <v>471558</v>
       </c>
@@ -6742,7 +6746,7 @@
         <v>1091</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="I68" s="39" t="s">
         <v>593</v>
@@ -6751,19 +6755,19 @@
         <v>69</v>
       </c>
       <c r="K68" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L68" t="s">
         <v>1092</v>
       </c>
       <c r="O68" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="P68" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="39">
         <v>574362</v>
       </c>
@@ -6795,13 +6799,13 @@
         <v>1098</v>
       </c>
       <c r="O69" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="P69" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="39">
         <v>528324</v>
       </c>
@@ -6833,7 +6837,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="39">
         <v>532292</v>
       </c>
@@ -6865,7 +6869,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="39">
         <v>528811</v>
       </c>
@@ -6891,19 +6895,19 @@
         <v>136</v>
       </c>
       <c r="K72" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L72" t="s">
         <v>1104</v>
       </c>
       <c r="O72" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="P72" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="39">
         <v>533396</v>
       </c>
@@ -6935,13 +6939,13 @@
         <v>1105</v>
       </c>
       <c r="O73" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="P73" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="39">
         <v>567493</v>
       </c>
@@ -6967,19 +6971,19 @@
         <v>171</v>
       </c>
       <c r="K74" s="39" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="L74" t="s">
         <v>1108</v>
       </c>
       <c r="O74" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="P74" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="39">
         <v>564857</v>
       </c>
@@ -7002,7 +7006,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="39">
         <v>567627</v>
       </c>
@@ -7025,7 +7029,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="39">
         <v>564566</v>
       </c>
@@ -7048,7 +7052,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="39">
         <v>564942</v>
       </c>
@@ -7071,7 +7075,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="39">
         <v>564662</v>
       </c>
@@ -7094,7 +7098,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="39">
         <v>564401</v>
       </c>
@@ -7117,7 +7121,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="39">
         <v>572411</v>
       </c>
@@ -7140,7 +7144,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="39">
         <v>563884</v>
       </c>
@@ -7163,7 +7167,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="39">
         <v>564322</v>
       </c>
@@ -7186,7 +7190,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="39">
         <v>471403</v>
       </c>
@@ -7209,7 +7213,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="39">
         <v>564333</v>
       </c>
@@ -7232,7 +7236,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="39">
         <v>572490</v>
       </c>
@@ -7255,7 +7259,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="39">
         <v>564476</v>
       </c>
@@ -7278,7 +7282,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="39">
         <v>563708</v>
       </c>
@@ -7301,7 +7305,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="39">
         <v>572482</v>
       </c>
@@ -7324,7 +7328,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="39">
         <v>471259</v>
       </c>
@@ -7347,15 +7351,15 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="39">
         <v>567570</v>
       </c>
       <c r="B91" s="62">
         <v>45294</v>
       </c>
-      <c r="C91" s="39" t="s">
-        <v>1046</v>
+      <c r="C91" s="74">
+        <v>45175</v>
       </c>
       <c r="D91" s="58">
         <v>0.3923611111111111</v>
@@ -7370,7 +7374,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="39">
         <v>522966</v>
       </c>
@@ -7393,7 +7397,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="39">
         <v>500534</v>
       </c>
@@ -7416,7 +7420,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="39">
         <v>563741</v>
       </c>
@@ -7439,15 +7443,15 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="39">
         <v>564354</v>
       </c>
       <c r="B95" s="62">
         <v>45272</v>
       </c>
-      <c r="C95" s="39" t="s">
-        <v>1046</v>
+      <c r="C95" s="74">
+        <v>45176</v>
       </c>
       <c r="D95" s="58">
         <v>0.39930555555555558</v>
@@ -7462,7 +7466,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="39">
         <v>603928</v>
       </c>
@@ -7485,15 +7489,15 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="39">
         <v>502414</v>
       </c>
       <c r="B97" s="62">
         <v>45272</v>
       </c>
-      <c r="C97" s="39" t="s">
-        <v>1046</v>
+      <c r="C97" s="74">
+        <v>44823</v>
       </c>
       <c r="D97" s="58">
         <v>0.44791666666666669</v>
@@ -7508,7 +7512,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="39">
         <v>471581</v>
       </c>
@@ -7531,15 +7535,15 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="39">
         <v>567510</v>
       </c>
       <c r="B99" s="62">
         <v>45247</v>
       </c>
-      <c r="C99" s="39" t="s">
-        <v>1046</v>
+      <c r="C99" s="74">
+        <v>45176</v>
       </c>
       <c r="D99" s="39" t="s">
         <v>1137</v>
@@ -7554,7 +7558,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="39">
         <v>564891</v>
       </c>
@@ -7577,7 +7581,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="39">
         <v>471841</v>
       </c>
@@ -7600,7 +7604,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="39">
         <v>567176</v>
       </c>
@@ -7623,7 +7627,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="39">
         <v>502446</v>
       </c>
@@ -7646,7 +7650,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="39">
         <v>563703</v>
       </c>
@@ -7666,10 +7670,10 @@
         <v>593</v>
       </c>
       <c r="L104" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="39">
         <v>564573</v>
       </c>
@@ -7689,10 +7693,10 @@
         <v>593</v>
       </c>
       <c r="L105" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="39">
         <v>564038</v>
       </c>
@@ -7715,7 +7719,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="39">
         <v>564593</v>
       </c>
@@ -7738,7 +7742,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="39">
         <v>567439</v>
       </c>
@@ -7761,7 +7765,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="39">
         <v>577864</v>
       </c>
@@ -7784,7 +7788,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="39">
         <v>498720</v>
       </c>
@@ -7807,7 +7811,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="39">
         <v>563721</v>
       </c>
@@ -7830,7 +7834,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="39">
         <v>603551</v>
       </c>
@@ -7853,7 +7857,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="39">
         <v>572673</v>
       </c>
@@ -7876,7 +7880,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="39">
         <v>471495</v>
       </c>
@@ -7899,7 +7903,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="39">
         <v>563788</v>
       </c>
@@ -7922,7 +7926,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="39">
         <v>563824</v>
       </c>
@@ -7945,7 +7949,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="39">
         <v>564740</v>
       </c>
@@ -7968,7 +7972,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="39">
         <v>567199</v>
       </c>
@@ -7991,7 +7995,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="39">
         <v>567221</v>
       </c>
@@ -8014,7 +8018,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="39">
         <v>564937</v>
       </c>
@@ -8037,7 +8041,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="39">
         <v>567116</v>
       </c>
@@ -8060,7 +8064,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="39">
         <v>471749</v>
       </c>
@@ -8083,7 +8087,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="39">
         <v>564842</v>
       </c>
@@ -8106,7 +8110,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="39">
         <v>567037</v>
       </c>
@@ -8129,7 +8133,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="39">
         <v>567200</v>
       </c>
@@ -8152,7 +8156,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="39">
         <v>564361</v>
       </c>
@@ -8175,7 +8179,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="39">
         <v>603692</v>
       </c>
@@ -8198,7 +8202,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="39">
         <v>578866</v>
       </c>
@@ -8221,7 +8225,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="39">
         <v>532142</v>
       </c>
@@ -8244,7 +8248,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="39">
         <v>578578</v>
       </c>
@@ -8267,7 +8271,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="39">
         <v>567565</v>
       </c>
@@ -8290,7 +8294,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="39">
         <v>532013</v>
       </c>
@@ -8313,7 +8317,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="39">
         <v>564665</v>
       </c>
@@ -8336,7 +8340,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="39">
         <v>569218</v>
       </c>
@@ -8359,7 +8363,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="39">
         <v>564318</v>
       </c>
@@ -8382,7 +8386,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="39">
         <v>564016</v>
       </c>
@@ -8405,7 +8409,7 @@
         <v>290823</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="39">
         <v>528653</v>
       </c>
@@ -8428,15 +8432,15 @@
         <v>280823</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="39">
         <v>567207</v>
       </c>
       <c r="B138" s="62">
         <v>45247</v>
       </c>
-      <c r="C138" s="39" t="s">
-        <v>1046</v>
+      <c r="C138" s="74">
+        <v>45175</v>
       </c>
       <c r="D138" s="39" t="s">
         <v>665</v>
@@ -8457,7 +8461,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="39">
         <v>563828</v>
       </c>
@@ -8480,7 +8484,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="39">
         <v>563764</v>
       </c>
@@ -8503,7 +8507,7 @@
         <v>230823</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="39">
         <v>532087</v>
       </c>
@@ -8526,7 +8530,7 @@
         <v>190923</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="39">
         <v>528707</v>
       </c>
@@ -8549,7 +8553,7 @@
         <v>290823</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="39">
         <v>500940</v>
       </c>
@@ -8569,21 +8573,21 @@
         <v>593</v>
       </c>
       <c r="L143" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="M143" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="39">
         <v>564319</v>
       </c>
       <c r="B144" s="62">
         <v>45246</v>
       </c>
-      <c r="C144" s="39" t="s">
-        <v>1046</v>
+      <c r="C144" s="74">
+        <v>45175</v>
       </c>
       <c r="D144" s="39" t="s">
         <v>635</v>
@@ -8595,13 +8599,13 @@
         <v>593</v>
       </c>
       <c r="L144" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M144" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="39">
         <v>563731</v>
       </c>
@@ -8615,7 +8619,7 @@
         <v>654</v>
       </c>
       <c r="E145" s="39" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="I145" s="39" t="s">
         <v>593</v>
@@ -8624,7 +8628,7 @@
         <v>230523</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="39">
         <v>563727</v>
       </c>
@@ -8638,7 +8642,7 @@
         <v>658</v>
       </c>
       <c r="E146" s="39" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I146" s="39" t="s">
         <v>593</v>
@@ -8647,7 +8651,7 @@
         <v>230823</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="39">
         <v>563712</v>
       </c>
@@ -8670,7 +8674,7 @@
         <v>230823</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="39">
         <v>563757</v>
       </c>
@@ -8693,7 +8697,7 @@
         <v>230823</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="39">
         <v>563702</v>
       </c>
@@ -8716,7 +8720,7 @@
         <v>230823</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="39">
         <v>578675</v>
       </c>
@@ -8730,7 +8734,7 @@
         <v>894</v>
       </c>
       <c r="E150" s="39" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I150" s="39" t="s">
         <v>593</v>
@@ -8739,15 +8743,15 @@
         <v>230823</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="39">
         <v>471823</v>
       </c>
       <c r="B151" s="62">
         <v>45247</v>
       </c>
-      <c r="C151" s="39" t="s">
-        <v>1046</v>
+      <c r="C151" s="74">
+        <v>45175</v>
       </c>
       <c r="D151" s="39" t="s">
         <v>893</v>
@@ -8765,7 +8769,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="39">
         <v>577946</v>
       </c>
@@ -8788,7 +8792,7 @@
         <v>150923</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="39">
         <v>514040</v>
       </c>
@@ -8808,10 +8812,10 @@
         <v>593</v>
       </c>
       <c r="L153" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="39">
         <v>577445</v>
       </c>
@@ -8831,10 +8835,10 @@
         <v>593</v>
       </c>
       <c r="L154" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="39">
         <v>569057</v>
       </c>
@@ -8857,7 +8861,7 @@
         <v>150923</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="39">
         <v>594136</v>
       </c>
@@ -8868,7 +8872,7 @@
         <v>1046</v>
       </c>
       <c r="D156" s="39" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E156" s="39" t="s">
         <v>1010</v>
@@ -8877,13 +8881,13 @@
         <v>593</v>
       </c>
       <c r="L156" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M156" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="39">
         <v>569147</v>
       </c>
@@ -8906,7 +8910,7 @@
         <v>150923</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="39">
         <v>564852</v>
       </c>
@@ -8917,7 +8921,7 @@
         <v>1046</v>
       </c>
       <c r="D158" s="39" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E158" s="39" t="s">
         <v>1010</v>
@@ -8926,13 +8930,13 @@
         <v>593</v>
       </c>
       <c r="L158" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M158" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="39">
         <v>567157</v>
       </c>
@@ -8955,7 +8959,7 @@
         <v>150923</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="39">
         <v>567224</v>
       </c>
@@ -8966,7 +8970,7 @@
         <v>1046</v>
       </c>
       <c r="D160" s="39" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E160" s="39" t="s">
         <v>1150</v>
@@ -8975,13 +8979,13 @@
         <v>593</v>
       </c>
       <c r="L160" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M160" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="39">
         <v>572426</v>
       </c>
@@ -9001,13 +9005,13 @@
         <v>593</v>
       </c>
       <c r="L161" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M161" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="39">
         <v>569073</v>
       </c>
@@ -9018,7 +9022,7 @@
         <v>1046</v>
       </c>
       <c r="D162" s="39" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E162" s="39" t="s">
         <v>1150</v>
@@ -9027,21 +9031,21 @@
         <v>593</v>
       </c>
       <c r="L162" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="M162" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="39">
         <v>471652</v>
       </c>
       <c r="B163" s="62">
         <v>45238</v>
       </c>
-      <c r="C163" s="39" t="s">
-        <v>1046</v>
+      <c r="C163" s="74">
+        <v>45175</v>
       </c>
       <c r="D163" s="39" t="s">
         <v>893</v>
@@ -9074,21 +9078,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K332"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="6" width="60.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.5703125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="23.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="35.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.453125" customWidth="1"/>
+    <col min="6" max="6" width="60.81640625" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.54296875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="23.54296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="35.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="65" t="s">
         <v>587</v>
       </c>
@@ -9103,7 +9107,7 @@
       <c r="J1" s="66"/>
       <c r="K1" s="67"/>
     </row>
-    <row r="2" spans="1:11" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
@@ -9138,7 +9142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
         <v>483841</v>
       </c>
@@ -9173,7 +9177,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18">
         <v>482046</v>
       </c>
@@ -9208,7 +9212,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>480898</v>
       </c>
@@ -9243,7 +9247,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
         <v>480705</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>480757</v>
       </c>
@@ -9313,7 +9317,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>480712</v>
       </c>
@@ -9348,7 +9352,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>527057</v>
       </c>
@@ -9383,7 +9387,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="18">
         <v>465564</v>
       </c>
@@ -9418,7 +9422,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18">
         <v>453730</v>
       </c>
@@ -9453,7 +9457,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="18">
         <v>480894</v>
       </c>
@@ -9488,7 +9492,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18">
         <v>550123</v>
       </c>
@@ -9523,7 +9527,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
         <v>480396</v>
       </c>
@@ -9558,7 +9562,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18">
         <v>204921</v>
       </c>
@@ -9593,7 +9597,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18">
         <v>206567</v>
       </c>
@@ -9628,7 +9632,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18">
         <v>206575</v>
       </c>
@@ -9663,7 +9667,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18">
         <v>550167</v>
       </c>
@@ -9698,7 +9702,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18">
         <v>480623</v>
       </c>
@@ -9733,7 +9737,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="18">
         <v>480667</v>
       </c>
@@ -9768,7 +9772,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="18">
         <v>550014</v>
       </c>
@@ -9803,7 +9807,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="18">
         <v>206562</v>
       </c>
@@ -9838,7 +9842,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18">
         <v>480591</v>
       </c>
@@ -9873,7 +9877,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18">
         <v>550036</v>
       </c>
@@ -9908,7 +9912,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18">
         <v>480692</v>
       </c>
@@ -9943,7 +9947,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="18">
         <v>480639</v>
       </c>
@@ -9978,7 +9982,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18">
         <v>550074</v>
       </c>
@@ -10013,7 +10017,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="18">
         <v>550194</v>
       </c>
@@ -10048,7 +10052,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18">
         <v>480601</v>
       </c>
@@ -10083,7 +10087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18">
         <v>41265</v>
       </c>
@@ -10118,7 +10122,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18">
         <v>206160</v>
       </c>
@@ -10153,7 +10157,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18">
         <v>207933</v>
       </c>
@@ -10188,7 +10192,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="18">
         <v>206632</v>
       </c>
@@ -10223,7 +10227,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="18">
         <v>204869</v>
       </c>
@@ -10258,7 +10262,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18">
         <v>455251</v>
       </c>
@@ -10293,7 +10297,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="18">
         <v>207368</v>
       </c>
@@ -10328,7 +10332,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="18">
         <v>447244</v>
       </c>
@@ -10363,7 +10367,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18">
         <v>204908</v>
       </c>
@@ -10398,7 +10402,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18">
         <v>408594</v>
       </c>
@@ -10433,7 +10437,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="18">
         <v>460375</v>
       </c>
@@ -10468,7 +10472,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="18">
         <v>460200</v>
       </c>
@@ -10503,7 +10507,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18">
         <v>460484</v>
       </c>
@@ -10538,7 +10542,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18">
         <v>460667</v>
       </c>
@@ -10573,7 +10577,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18">
         <v>459116</v>
       </c>
@@ -10608,7 +10612,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="18">
         <v>459306</v>
       </c>
@@ -10643,7 +10647,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="18">
         <v>438121</v>
       </c>
@@ -10678,7 +10682,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18">
         <v>416359</v>
       </c>
@@ -10713,7 +10717,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="18">
         <v>42646</v>
       </c>
@@ -10748,7 +10752,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>205424</v>
       </c>
@@ -10783,7 +10787,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
         <v>205425</v>
       </c>
@@ -10818,7 +10822,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>460739</v>
       </c>
@@ -10853,7 +10857,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18">
         <v>414933</v>
       </c>
@@ -10888,7 +10892,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18">
         <v>42709</v>
       </c>
@@ -10923,7 +10927,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="18">
         <v>455393</v>
       </c>
@@ -10958,7 +10962,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18">
         <v>44347</v>
       </c>
@@ -10993,7 +10997,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="18">
         <v>414880</v>
       </c>
@@ -11028,7 +11032,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18">
         <v>480952</v>
       </c>
@@ -11063,7 +11067,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="18">
         <v>414230</v>
       </c>
@@ -11098,7 +11102,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="18">
         <v>40516</v>
       </c>
@@ -11133,7 +11137,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18" t="s">
         <v>766</v>
       </c>
@@ -11168,7 +11172,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="18">
         <v>552159</v>
       </c>
@@ -11203,7 +11207,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="18">
         <v>552489</v>
       </c>
@@ -11238,7 +11242,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18">
         <v>552428</v>
       </c>
@@ -11273,7 +11277,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="28">
         <v>552282</v>
       </c>
@@ -11308,7 +11312,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="27">
         <v>552132</v>
       </c>
@@ -11343,7 +11347,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="18">
         <v>552444</v>
       </c>
@@ -11378,7 +11382,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="18" t="s">
         <v>766</v>
       </c>
@@ -11413,7 +11417,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18">
         <v>552006</v>
       </c>
@@ -11448,7 +11452,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="18">
         <v>552051</v>
       </c>
@@ -11483,7 +11487,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="18">
         <v>553350</v>
       </c>
@@ -11518,7 +11522,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="71" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="18">
         <v>552014</v>
       </c>
@@ -11553,7 +11557,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="18">
         <v>553507</v>
       </c>
@@ -11588,7 +11592,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="18">
         <v>553430</v>
       </c>
@@ -11623,7 +11627,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="18">
         <v>553853</v>
       </c>
@@ -11658,7 +11662,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="18">
         <v>554419</v>
       </c>
@@ -11693,7 +11697,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="18">
         <v>206566</v>
       </c>
@@ -11728,7 +11732,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="18">
         <v>554798</v>
       </c>
@@ -11763,7 +11767,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="18">
         <v>553675</v>
       </c>
@@ -11798,7 +11802,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="18">
         <v>553597</v>
       </c>
@@ -11833,7 +11837,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="18">
         <v>553023</v>
       </c>
@@ -11868,7 +11872,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="18">
         <v>553671</v>
       </c>
@@ -11903,7 +11907,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="18">
         <v>553378</v>
       </c>
@@ -11938,7 +11942,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="83" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="18">
         <v>552758</v>
       </c>
@@ -11973,7 +11977,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="84" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="18">
         <v>553519</v>
       </c>
@@ -12008,7 +12012,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="85" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="18">
         <v>553500</v>
       </c>
@@ -12043,7 +12047,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="18">
         <v>552826</v>
       </c>
@@ -12078,7 +12082,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="87" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="18">
         <v>553967</v>
       </c>
@@ -12113,7 +12117,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="18">
         <v>553399</v>
       </c>
@@ -12148,7 +12152,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="89" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="18">
         <v>552293</v>
       </c>
@@ -12183,7 +12187,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="90" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="18">
         <v>553900</v>
       </c>
@@ -12218,7 +12222,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="91" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="18">
         <v>554500</v>
       </c>
@@ -12253,7 +12257,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="18">
         <v>552456</v>
       </c>
@@ -12288,7 +12292,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="93" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="18">
         <v>554001</v>
       </c>
@@ -12323,7 +12327,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="18">
         <v>554610</v>
       </c>
@@ -12358,7 +12362,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="18">
         <v>553089</v>
       </c>
@@ -12393,7 +12397,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="96" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="18">
         <v>554021</v>
       </c>
@@ -12428,7 +12432,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="18">
         <v>553369</v>
       </c>
@@ -12463,7 +12467,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="2" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" s="2" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="18">
         <v>554416</v>
       </c>
@@ -12498,7 +12502,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="30">
         <v>553467</v>
       </c>
@@ -12533,7 +12537,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="18">
         <v>552683</v>
       </c>
@@ -12568,7 +12572,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="18">
         <v>554713</v>
       </c>
@@ -12603,7 +12607,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="18">
         <v>552588</v>
       </c>
@@ -12638,7 +12642,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="18">
         <v>482292</v>
       </c>
@@ -12673,7 +12677,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="27">
         <v>554694</v>
       </c>
@@ -12708,7 +12712,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="27">
         <v>554687</v>
       </c>
@@ -12743,7 +12747,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="9">
         <v>554718</v>
       </c>
@@ -12778,7 +12782,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>552085</v>
       </c>
@@ -12813,7 +12817,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>554722</v>
       </c>
@@ -12848,7 +12852,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="50">
         <v>554792</v>
       </c>
@@ -12883,7 +12887,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>554067</v>
       </c>
@@ -12918,7 +12922,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="9">
         <v>552463</v>
       </c>
@@ -12953,7 +12957,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="9">
         <v>554410</v>
       </c>
@@ -12988,7 +12992,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="9">
         <v>207185</v>
       </c>
@@ -13023,7 +13027,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="9">
         <v>551130</v>
       </c>
@@ -13058,7 +13062,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>553976</v>
       </c>
@@ -13093,7 +13097,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="9">
         <v>552390</v>
       </c>
@@ -13128,7 +13132,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="9">
         <v>554228</v>
       </c>
@@ -13163,7 +13167,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>554626</v>
       </c>
@@ -13198,7 +13202,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>554063</v>
       </c>
@@ -13233,7 +13237,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="9">
         <v>552817</v>
       </c>
@@ -13268,7 +13272,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="9">
         <v>553909</v>
       </c>
@@ -13303,7 +13307,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>552010</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>553679</v>
       </c>
@@ -13373,7 +13377,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>553247</v>
       </c>
@@ -13408,7 +13412,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="9">
         <v>551097</v>
       </c>
@@ -13443,7 +13447,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="9">
         <v>552867</v>
       </c>
@@ -13478,7 +13482,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>554891</v>
       </c>
@@ -13513,7 +13517,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>551214</v>
       </c>
@@ -13548,7 +13552,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>554518</v>
       </c>
@@ -13583,7 +13587,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="9">
         <v>554699</v>
       </c>
@@ -13618,7 +13622,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="9">
         <v>554550</v>
       </c>
@@ -13653,7 +13657,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>552081</v>
       </c>
@@ -13688,7 +13692,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>553280</v>
       </c>
@@ -13723,7 +13727,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="9">
         <v>551142</v>
       </c>
@@ -13758,7 +13762,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="9">
         <v>554402</v>
       </c>
@@ -13793,7 +13797,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>553019</v>
       </c>
@@ -13828,7 +13832,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>554869</v>
       </c>
@@ -13863,7 +13867,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>553003</v>
       </c>
@@ -13898,7 +13902,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="9">
         <v>554994</v>
       </c>
@@ -13933,7 +13937,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="9">
         <v>553795</v>
       </c>
@@ -13968,7 +13972,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>552635</v>
       </c>
@@ -14003,7 +14007,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>554678</v>
       </c>
@@ -14038,7 +14042,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="9">
         <v>554654</v>
       </c>
@@ -14073,7 +14077,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="9">
         <v>554437</v>
       </c>
@@ -14108,7 +14112,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="9">
         <v>552318</v>
       </c>
@@ -14143,7 +14147,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="9">
         <v>552975</v>
       </c>
@@ -14178,7 +14182,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>552378</v>
       </c>
@@ -14213,7 +14217,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>554103</v>
       </c>
@@ -14248,7 +14252,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="9">
         <v>551110</v>
       </c>
@@ -14283,7 +14287,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="9">
         <v>552845</v>
       </c>
@@ -14318,7 +14322,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>554485</v>
       </c>
@@ -14353,7 +14357,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="9">
         <v>41118</v>
       </c>
@@ -14388,7 +14392,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="9">
         <v>552271</v>
       </c>
@@ -14423,7 +14427,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>554603</v>
       </c>
@@ -14458,7 +14462,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>552707</v>
       </c>
@@ -14493,7 +14497,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="9">
         <v>554926</v>
       </c>
@@ -14528,7 +14532,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="9">
         <v>554941</v>
       </c>
@@ -14563,7 +14567,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>552243</v>
       </c>
@@ -14598,7 +14602,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>553947</v>
       </c>
@@ -14633,7 +14637,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>554885</v>
       </c>
@@ -14668,7 +14672,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="9">
         <v>554368</v>
       </c>
@@ -14703,7 +14707,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="9">
         <v>553403</v>
       </c>
@@ -14738,7 +14742,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="9">
         <v>553314</v>
       </c>
@@ -14773,7 +14777,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="9">
         <v>553511</v>
       </c>
@@ -14808,7 +14812,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>553962</v>
       </c>
@@ -14843,7 +14847,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="9">
         <v>553422</v>
       </c>
@@ -14878,7 +14882,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="9">
         <v>553929</v>
       </c>
@@ -14913,7 +14917,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>554261</v>
       </c>
@@ -14948,7 +14952,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="9">
         <v>554430</v>
       </c>
@@ -14983,7 +14987,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="9">
         <v>552305</v>
       </c>
@@ -15018,7 +15022,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>554015</v>
       </c>
@@ -15053,7 +15057,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="9">
         <v>552177</v>
       </c>
@@ -15088,7 +15092,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="9">
         <v>554579</v>
       </c>
@@ -15123,7 +15127,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>554677</v>
       </c>
@@ -15158,7 +15162,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="9">
         <v>554300</v>
       </c>
@@ -15193,7 +15197,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="9">
         <v>554810</v>
       </c>
@@ -15228,7 +15232,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="9">
         <v>553686</v>
       </c>
@@ -15263,7 +15267,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="9">
         <v>552341</v>
       </c>
@@ -15298,7 +15302,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>553826</v>
       </c>
@@ -15333,7 +15337,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="9">
         <v>554802</v>
       </c>
@@ -15368,7 +15372,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="9">
         <v>554313</v>
       </c>
@@ -15403,7 +15407,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>553562</v>
       </c>
@@ -15438,7 +15442,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="9">
         <v>554468</v>
       </c>
@@ -15473,7 +15477,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="9">
         <v>552673</v>
       </c>
@@ -15508,7 +15512,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="9">
         <v>553230</v>
       </c>
@@ -15543,7 +15547,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="9">
         <v>554761</v>
       </c>
@@ -15578,7 +15582,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>552056</v>
       </c>
@@ -15613,7 +15617,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="9">
         <v>553910</v>
       </c>
@@ -15648,7 +15652,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="9">
         <v>552437</v>
       </c>
@@ -15683,7 +15687,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="9">
         <v>553265</v>
       </c>
@@ -15718,7 +15722,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="9">
         <v>554600</v>
       </c>
@@ -15753,7 +15757,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>553670</v>
       </c>
@@ -15788,7 +15792,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="9">
         <v>554393</v>
       </c>
@@ -15823,7 +15827,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="9">
         <v>552828</v>
       </c>
@@ -15858,7 +15862,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="9">
         <v>551067</v>
       </c>
@@ -15893,7 +15897,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="9">
         <v>552330</v>
       </c>
@@ -15928,7 +15932,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="9">
         <v>554918</v>
       </c>
@@ -15963,7 +15967,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="9">
         <v>552229</v>
       </c>
@@ -15998,7 +16002,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="9">
         <v>552112</v>
       </c>
@@ -16033,7 +16037,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="9">
         <v>553178</v>
       </c>
@@ -16068,7 +16072,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="9">
         <v>554682</v>
       </c>
@@ -16103,7 +16107,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="9">
         <v>551047</v>
       </c>
@@ -16138,7 +16142,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="9">
         <v>553789</v>
       </c>
@@ -16173,7 +16177,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="9">
         <v>551123</v>
       </c>
@@ -16208,7 +16212,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="9">
         <v>554878</v>
       </c>
@@ -16243,7 +16247,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="9">
         <v>553949</v>
       </c>
@@ -16278,7 +16282,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="9">
         <v>552854</v>
       </c>
@@ -16313,7 +16317,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="9">
         <v>552176</v>
       </c>
@@ -16348,7 +16352,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="9">
         <v>552443</v>
       </c>
@@ -16383,7 +16387,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="9">
         <v>553147</v>
       </c>
@@ -16418,7 +16422,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="9">
         <v>553118</v>
       </c>
@@ -16453,7 +16457,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="9">
         <v>552092</v>
       </c>
@@ -16488,7 +16492,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="9">
         <v>553210</v>
       </c>
@@ -16523,7 +16527,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="9">
         <v>554379</v>
       </c>
@@ -16558,7 +16562,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="9">
         <v>552771</v>
       </c>
@@ -16593,7 +16597,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="9">
         <v>552882</v>
       </c>
@@ -16628,7 +16632,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="9">
         <v>553212</v>
       </c>
@@ -16663,7 +16667,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="9">
         <v>554781</v>
       </c>
@@ -16698,7 +16702,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="9">
         <v>553405</v>
       </c>
@@ -16733,7 +16737,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="9">
         <v>552616</v>
       </c>
@@ -16768,7 +16772,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="9">
         <v>554077</v>
       </c>
@@ -16803,7 +16807,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="9">
         <v>554050</v>
       </c>
@@ -16838,7 +16842,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="9">
         <v>554834</v>
       </c>
@@ -16873,7 +16877,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="9">
         <v>552419</v>
       </c>
@@ -16908,7 +16912,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="9">
         <v>552395</v>
       </c>
@@ -16943,7 +16947,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="9">
         <v>552583</v>
       </c>
@@ -16978,7 +16982,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="9">
         <v>554877</v>
       </c>
@@ -17013,7 +17017,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="9">
         <v>552818</v>
       </c>
@@ -17048,7 +17052,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="9">
         <v>551063</v>
       </c>
@@ -17083,7 +17087,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="9">
         <v>552992</v>
       </c>
@@ -17118,7 +17122,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="9">
         <v>552939</v>
       </c>
@@ -17153,7 +17157,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="9">
         <v>554011</v>
       </c>
@@ -17188,7 +17192,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="9">
         <v>207798</v>
       </c>
@@ -17223,7 +17227,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="9">
         <v>553520</v>
       </c>
@@ -17258,7 +17262,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="9">
         <v>552668</v>
       </c>
@@ -17293,7 +17297,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="9">
         <v>552391</v>
       </c>
@@ -17328,7 +17332,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="9">
         <v>552439</v>
       </c>
@@ -17363,7 +17367,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="9">
         <v>553269</v>
       </c>
@@ -17398,7 +17402,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="9">
         <v>40597</v>
       </c>
@@ -17433,7 +17437,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="9">
         <v>552780</v>
       </c>
@@ -17468,7 +17472,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="9">
         <v>531021</v>
       </c>
@@ -17503,7 +17507,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="9">
         <v>554872</v>
       </c>
@@ -17538,7 +17542,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="9">
         <v>552020</v>
       </c>
@@ -17573,7 +17577,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="9">
         <v>552644</v>
       </c>
@@ -17608,7 +17612,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="9">
         <v>554591</v>
       </c>
@@ -17643,7 +17647,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="9">
         <v>554800</v>
       </c>
@@ -17678,7 +17682,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="9">
         <v>552319</v>
       </c>
@@ -17713,7 +17717,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="9">
         <v>554358</v>
       </c>
@@ -17748,7 +17752,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" s="9">
         <v>553248</v>
       </c>
@@ -17783,7 +17787,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" s="9">
         <v>553706</v>
       </c>
@@ -17818,7 +17822,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" s="9">
         <v>552436</v>
       </c>
@@ -17853,7 +17857,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="9">
         <v>553033</v>
       </c>
@@ -17888,7 +17892,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="9">
         <v>554519</v>
       </c>
@@ -17923,7 +17927,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="9">
         <v>552655</v>
       </c>
@@ -17958,7 +17962,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="9">
         <v>553774</v>
       </c>
@@ -17993,7 +17997,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="9">
         <v>553869</v>
       </c>
@@ -18028,7 +18032,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="9">
         <v>553162</v>
       </c>
@@ -18063,7 +18067,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="9">
         <v>553344</v>
       </c>
@@ -18098,7 +18102,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="9">
         <v>553238</v>
       </c>
@@ -18133,7 +18137,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="9">
         <v>554691</v>
       </c>
@@ -18168,7 +18172,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="9">
         <v>551117</v>
       </c>
@@ -18203,7 +18207,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="9">
         <v>551044</v>
       </c>
@@ -18238,7 +18242,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="9">
         <v>553628</v>
       </c>
@@ -18273,7 +18277,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" s="9">
         <v>553645</v>
       </c>
@@ -18308,7 +18312,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" s="9">
         <v>553217</v>
       </c>
@@ -18343,7 +18347,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" s="9">
         <v>552084</v>
       </c>
@@ -18378,7 +18382,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" s="9">
         <v>554488</v>
       </c>
@@ -18413,7 +18417,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A268" s="9">
         <v>553820</v>
       </c>
@@ -18448,7 +18452,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A269" s="9">
         <v>554454</v>
       </c>
@@ -18483,7 +18487,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A270" s="9">
         <v>552377</v>
       </c>
@@ -18518,7 +18522,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A271" s="9">
         <v>551200</v>
       </c>
@@ -18553,7 +18557,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" s="9">
         <v>554028</v>
       </c>
@@ -18588,7 +18592,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" s="9">
         <v>553653</v>
       </c>
@@ -18623,7 +18627,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" s="9">
         <v>552127</v>
       </c>
@@ -18658,7 +18662,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" s="9">
         <v>554309</v>
       </c>
@@ -18693,7 +18697,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" s="9">
         <v>551145</v>
       </c>
@@ -18728,7 +18732,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" s="9">
         <v>551188</v>
       </c>
@@ -18763,7 +18767,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" s="9">
         <v>554605</v>
       </c>
@@ -18798,7 +18802,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" s="9">
         <v>551167</v>
       </c>
@@ -18833,7 +18837,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" s="9">
         <v>552524</v>
       </c>
@@ -18868,7 +18872,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" s="9">
         <v>553304</v>
       </c>
@@ -18903,7 +18907,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" s="9">
         <v>552345</v>
       </c>
@@ -18938,7 +18942,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" s="9">
         <v>552435</v>
       </c>
@@ -18973,7 +18977,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" s="9">
         <v>554844</v>
       </c>
@@ -19008,7 +19012,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" s="9">
         <v>551051</v>
       </c>
@@ -19043,7 +19047,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" s="9">
         <v>552033</v>
       </c>
@@ -19078,7 +19082,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" s="9">
         <v>552961</v>
       </c>
@@ -19113,7 +19117,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" s="9">
         <v>554100</v>
       </c>
@@ -19148,7 +19152,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" s="9">
         <v>553251</v>
       </c>
@@ -19183,7 +19187,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" s="9">
         <v>552236</v>
       </c>
@@ -19218,7 +19222,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" s="9">
         <v>552039</v>
       </c>
@@ -19253,7 +19257,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" s="9">
         <v>553043</v>
       </c>
@@ -19288,7 +19292,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" s="9">
         <v>554297</v>
       </c>
@@ -19323,7 +19327,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" s="9">
         <v>553039</v>
       </c>
@@ -19358,7 +19362,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" s="9">
         <v>554208</v>
       </c>
@@ -19393,7 +19397,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" s="9">
         <v>552304</v>
       </c>
@@ -19428,7 +19432,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" s="9">
         <v>554375</v>
       </c>
@@ -19463,7 +19467,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" s="9">
         <v>554223</v>
       </c>
@@ -19498,7 +19502,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" s="9">
         <v>554487</v>
       </c>
@@ -19533,7 +19537,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" s="9">
         <v>551005</v>
       </c>
@@ -19568,7 +19572,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" s="9">
         <v>552476</v>
       </c>
@@ -19603,7 +19607,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" s="9">
         <v>553995</v>
       </c>
@@ -19638,7 +19642,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" s="9">
         <v>552768</v>
       </c>
@@ -19673,7 +19677,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" s="9">
         <v>551016</v>
       </c>
@@ -19708,7 +19712,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" s="9">
         <v>554018</v>
       </c>
@@ -19743,7 +19747,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" s="9">
         <v>552218</v>
       </c>
@@ -19778,7 +19782,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" s="9">
         <v>552589</v>
       </c>
@@ -19813,7 +19817,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" s="9">
         <v>553632</v>
       </c>
@@ -19848,7 +19852,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" s="9">
         <v>552723</v>
       </c>
@@ -19883,7 +19887,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" s="9">
         <v>553463</v>
       </c>
@@ -19918,7 +19922,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" s="9">
         <v>554123</v>
       </c>
@@ -19953,7 +19957,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" s="9">
         <v>554581</v>
       </c>
@@ -19988,7 +19992,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" s="9">
         <v>554706</v>
       </c>
@@ -20023,7 +20027,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" s="9">
         <v>207565</v>
       </c>
@@ -20058,7 +20062,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" s="9">
         <v>550105</v>
       </c>
@@ -20093,7 +20097,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" s="9">
         <v>414113</v>
       </c>
@@ -20128,7 +20132,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" s="9">
         <v>554742</v>
       </c>
@@ -20163,7 +20167,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" s="9">
         <v>531038</v>
       </c>
@@ -20198,7 +20202,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" s="9">
         <v>205332</v>
       </c>
@@ -20233,7 +20237,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" s="41">
         <v>527460</v>
       </c>
@@ -20268,7 +20272,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A321" s="56">
         <v>482957</v>
       </c>
@@ -20303,7 +20307,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A322" s="38">
         <v>481478</v>
       </c>
@@ -20338,7 +20342,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A323" s="38">
         <v>41282</v>
       </c>
@@ -20373,7 +20377,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A324" s="38">
         <v>459330</v>
       </c>
@@ -20408,7 +20412,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A325" s="38">
         <v>531502</v>
       </c>
@@ -20443,7 +20447,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A326" s="38">
         <v>41603</v>
       </c>
@@ -20478,7 +20482,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A327" s="38"/>
       <c r="B327" s="38"/>
       <c r="C327" s="38"/>
@@ -20491,7 +20495,7 @@
       <c r="J327" s="38"/>
       <c r="K327" s="38"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A328" s="38"/>
       <c r="B328" s="38"/>
       <c r="C328" s="38"/>
@@ -20504,7 +20508,7 @@
       <c r="J328" s="38"/>
       <c r="K328" s="38"/>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A329" s="38"/>
       <c r="B329" s="38"/>
       <c r="C329" s="38"/>
@@ -20517,7 +20521,7 @@
       <c r="J329" s="38"/>
       <c r="K329" s="38"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A330" s="38"/>
       <c r="B330" s="38"/>
       <c r="C330" s="38"/>
@@ -20530,7 +20534,7 @@
       <c r="J330" s="38"/>
       <c r="K330" s="38"/>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A331" s="38"/>
       <c r="B331" s="38"/>
       <c r="C331" s="38"/>
@@ -20543,7 +20547,7 @@
       <c r="J331" s="38"/>
       <c r="K331" s="38"/>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A332" s="38"/>
       <c r="B332" s="38"/>
       <c r="C332" s="38"/>
@@ -20570,7 +20574,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC3D4A4-DE02-4412-9979-0F23DB8D25A3}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20582,20 +20586,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="57.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="35.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1"/>
+    <col min="5" max="5" width="57.453125" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="35.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22">
         <v>43684</v>
       </c>
@@ -20610,7 +20614,7 @@
       <c r="H1" s="70"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
@@ -20639,7 +20643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
         <v>449455</v>
       </c>
@@ -20666,7 +20670,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18">
         <v>450645</v>
       </c>
@@ -20693,7 +20697,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>442944</v>
       </c>
@@ -20720,7 +20724,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
         <v>449321</v>
       </c>
@@ -20747,7 +20751,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>450805</v>
       </c>
@@ -20776,7 +20780,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>442815</v>
       </c>
@@ -20803,7 +20807,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>445366</v>
       </c>
@@ -20830,7 +20834,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="18">
         <v>449132</v>
       </c>
@@ -20855,7 +20859,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18">
         <v>445535</v>
       </c>
@@ -20880,7 +20884,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="18">
         <v>442103</v>
       </c>
@@ -20905,7 +20909,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18">
         <v>445246</v>
       </c>
@@ -20930,7 +20934,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
         <v>450388</v>
       </c>
@@ -20955,7 +20959,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18">
         <v>445385</v>
       </c>
@@ -20980,7 +20984,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18">
         <v>445544</v>
       </c>
@@ -21005,7 +21009,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18">
         <v>450542</v>
       </c>
@@ -21030,7 +21034,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18">
         <v>445556</v>
       </c>
@@ -21055,7 +21059,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18">
         <v>449480</v>
       </c>
@@ -21080,7 +21084,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="18">
         <v>450664</v>
       </c>
@@ -21105,7 +21109,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="18">
         <v>445087</v>
       </c>
@@ -21130,7 +21134,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="18">
         <v>442822</v>
       </c>
@@ -21155,7 +21159,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18">
         <v>450032</v>
       </c>
@@ -21180,7 +21184,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18">
         <v>442954</v>
       </c>
@@ -21205,7 +21209,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18">
         <v>449380</v>
       </c>
@@ -21230,7 +21234,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="18">
         <v>442727</v>
       </c>
@@ -21255,7 +21259,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18">
         <v>442000</v>
       </c>
@@ -21280,7 +21284,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="18">
         <v>451582</v>
       </c>
@@ -21305,7 +21309,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18">
         <v>450627</v>
       </c>
@@ -21330,7 +21334,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18">
         <v>438742</v>
       </c>
@@ -21357,7 +21361,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18">
         <v>443922</v>
       </c>
@@ -21384,7 +21388,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18">
         <v>438411</v>
       </c>
@@ -21411,7 +21415,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="18">
         <v>438687</v>
       </c>
@@ -21438,7 +21442,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="18">
         <v>438897</v>
       </c>
@@ -21465,7 +21469,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18">
         <v>438662</v>
       </c>
@@ -21492,7 +21496,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="18">
         <v>438969</v>
       </c>
@@ -21519,7 +21523,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="18">
         <v>438877</v>
       </c>
@@ -21546,7 +21550,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18">
         <v>438889</v>
       </c>
@@ -21573,7 +21577,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18">
         <v>443946</v>
       </c>
@@ -21600,7 +21604,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="18">
         <v>443903</v>
       </c>
@@ -21627,7 +21631,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="18">
         <v>4575</v>
       </c>
@@ -21654,7 +21658,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18">
         <v>44186</v>
       </c>
@@ -21681,7 +21685,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18">
         <v>4575</v>
       </c>
@@ -21708,7 +21712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18">
         <v>443926</v>
       </c>
@@ -21735,7 +21739,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="18">
         <v>438666</v>
       </c>
@@ -21762,7 +21766,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="18">
         <v>445100</v>
       </c>
@@ -21789,7 +21793,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18">
         <v>44217</v>
       </c>
@@ -21816,7 +21820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="18">
         <v>441801</v>
       </c>
@@ -21843,7 +21847,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>455333</v>
       </c>
@@ -21870,7 +21874,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
         <v>450104</v>
       </c>
@@ -21895,7 +21899,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>34613</v>
       </c>
@@ -21922,7 +21926,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18">
         <v>459121</v>
       </c>
@@ -21949,7 +21953,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18">
         <v>34429</v>
       </c>
@@ -21976,7 +21980,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="18">
         <v>459126</v>
       </c>
@@ -22001,7 +22005,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18">
         <v>34340</v>
       </c>
@@ -22028,7 +22032,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="18">
         <v>446597</v>
       </c>
@@ -22055,7 +22059,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18">
         <v>452393</v>
       </c>
@@ -22082,7 +22086,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="18">
         <v>438680</v>
       </c>
@@ -22109,7 +22113,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="18">
         <v>43983</v>
       </c>
@@ -22136,7 +22140,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18">
         <v>4575</v>
       </c>
@@ -22163,7 +22167,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="18">
         <v>4575</v>
       </c>
@@ -22190,7 +22194,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="18">
         <v>415483</v>
       </c>
@@ -22217,7 +22221,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18">
         <v>416516</v>
       </c>
@@ -22244,7 +22248,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="28">
         <v>416345</v>
       </c>
@@ -22271,7 +22275,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="27">
         <v>34171</v>
       </c>
@@ -22298,7 +22302,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="18">
         <v>416352</v>
       </c>
@@ -22325,7 +22329,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="18">
         <v>44790</v>
       </c>
@@ -22352,7 +22356,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18">
         <v>455068</v>
       </c>
@@ -22379,7 +22383,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="18">
         <v>455602</v>
       </c>
@@ -22406,7 +22410,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="18">
         <v>455976</v>
       </c>
@@ -22433,7 +22437,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="18">
         <v>460094</v>
       </c>
@@ -22460,7 +22464,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="18">
         <v>416653</v>
       </c>
@@ -22487,7 +22491,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="18">
         <v>34586</v>
       </c>
@@ -22514,7 +22518,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="18">
         <v>452940</v>
       </c>
@@ -22541,7 +22545,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="18">
         <v>416691</v>
       </c>
@@ -22568,7 +22572,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="18">
         <v>459703</v>
       </c>
@@ -22595,7 +22599,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="18">
         <v>4575</v>
       </c>
@@ -22620,7 +22624,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="18">
         <v>4575</v>
       </c>
@@ -22645,7 +22649,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="18">
         <v>452653</v>
       </c>
@@ -22672,7 +22676,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="18">
         <v>4575</v>
       </c>
@@ -22699,7 +22703,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="18">
         <v>459394</v>
       </c>
@@ -22726,7 +22730,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="18">
         <v>456401</v>
       </c>
@@ -22753,7 +22757,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="18">
         <v>452321</v>
       </c>
@@ -22780,7 +22784,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="18">
         <v>443959</v>
       </c>
@@ -22807,7 +22811,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="18">
         <v>459364</v>
       </c>
@@ -22834,7 +22838,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="18">
         <v>432950</v>
       </c>
@@ -22861,7 +22865,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="18">
         <v>414708</v>
       </c>
@@ -22887,7 +22891,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="18">
         <v>452549</v>
       </c>
@@ -22914,7 +22918,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="18">
         <v>459943</v>
       </c>
@@ -22941,7 +22945,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="18">
         <v>456629</v>
       </c>
@@ -22968,7 +22972,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="18">
         <v>459975</v>
       </c>
@@ -22993,7 +22997,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="18">
         <v>459985</v>
       </c>
@@ -23020,7 +23024,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="18">
         <v>414789</v>
       </c>
@@ -23047,7 +23051,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="18">
         <v>414703</v>
       </c>
@@ -23074,7 +23078,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="18">
         <v>416636</v>
       </c>
@@ -23101,7 +23105,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="18">
         <v>460329</v>
       </c>
@@ -23128,7 +23132,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="97" spans="1:14" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="18">
         <v>460003</v>
       </c>
@@ -23155,7 +23159,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="98" spans="1:14" s="2" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" s="2" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="18">
         <v>414521</v>
       </c>
@@ -23182,7 +23186,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="30">
         <v>459313</v>
       </c>
@@ -23209,7 +23213,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="18">
         <v>414867</v>
       </c>
@@ -23241,7 +23245,7 @@
       <c r="M100" s="39"/>
       <c r="N100" s="39"/>
     </row>
-    <row r="101" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="18">
         <v>445793</v>
       </c>
@@ -23273,7 +23277,7 @@
       <c r="M101" s="39"/>
       <c r="N101" s="39"/>
     </row>
-    <row r="102" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="18">
         <v>455750</v>
       </c>
@@ -23305,7 +23309,7 @@
       <c r="M102" s="39"/>
       <c r="N102" s="39"/>
     </row>
-    <row r="103" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="18">
         <v>34493</v>
       </c>
@@ -23337,7 +23341,7 @@
       <c r="M103" s="39"/>
       <c r="N103" s="39"/>
     </row>
-    <row r="104" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="27">
         <v>44639</v>
       </c>
@@ -23369,7 +23373,7 @@
       <c r="M104" s="39"/>
       <c r="N104" s="39"/>
     </row>
-    <row r="105" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="27">
         <v>4575</v>
       </c>
@@ -23401,7 +23405,7 @@
       <c r="M105" s="39"/>
       <c r="N105" s="39"/>
     </row>
-    <row r="106" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="9">
         <v>455887</v>
       </c>
@@ -23433,7 +23437,7 @@
       <c r="M106" s="39"/>
       <c r="N106" s="39"/>
     </row>
-    <row r="107" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>414738</v>
       </c>
@@ -23465,7 +23469,7 @@
       <c r="M107" s="39"/>
       <c r="N107" s="39"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="38">
         <v>416466</v>
       </c>
@@ -23497,7 +23501,7 @@
       <c r="M108" s="39"/>
       <c r="N108" s="39"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="38">
         <v>460183</v>
       </c>
@@ -23529,7 +23533,7 @@
       <c r="M109" s="39"/>
       <c r="N109" s="39"/>
     </row>
-    <row r="110" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="41">
         <v>408257</v>
       </c>
@@ -23561,7 +23565,7 @@
       <c r="M110" s="39"/>
       <c r="N110" s="39"/>
     </row>
-    <row r="111" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="41">
         <v>111617</v>
       </c>
@@ -23593,7 +23597,7 @@
       <c r="M111" s="39"/>
       <c r="N111" s="39"/>
     </row>
-    <row r="112" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="41">
         <v>4575</v>
       </c>
@@ -23625,7 +23629,7 @@
       <c r="M112" s="39"/>
       <c r="N112" s="39"/>
     </row>
-    <row r="113" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="41">
         <v>111602</v>
       </c>
@@ -23657,7 +23661,7 @@
       <c r="M113" s="39"/>
       <c r="N113" s="39"/>
     </row>
-    <row r="114" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="41">
         <v>4575</v>
       </c>
@@ -23689,7 +23693,7 @@
       <c r="M114" s="39"/>
       <c r="N114" s="39"/>
     </row>
-    <row r="115" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="41">
         <v>4575</v>
       </c>
@@ -23721,7 +23725,7 @@
       <c r="M115" s="39"/>
       <c r="N115" s="39"/>
     </row>
-    <row r="116" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="41">
         <v>111660</v>
       </c>
@@ -23753,7 +23757,7 @@
       <c r="M116" s="39"/>
       <c r="N116" s="39"/>
     </row>
-    <row r="117" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="41">
         <v>111608</v>
       </c>
@@ -23785,7 +23789,7 @@
       <c r="M117" s="39"/>
       <c r="N117" s="39"/>
     </row>
-    <row r="118" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="41"/>
       <c r="B118" s="41"/>
       <c r="C118" s="41"/>
@@ -23801,7 +23805,7 @@
       <c r="M118" s="39"/>
       <c r="N118" s="39"/>
     </row>
-    <row r="119" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="41"/>
       <c r="B119" s="41"/>
       <c r="C119" s="41"/>
@@ -23817,7 +23821,7 @@
       <c r="M119" s="39"/>
       <c r="N119" s="39"/>
     </row>
-    <row r="120" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="41"/>
       <c r="B120" s="41"/>
       <c r="C120" s="41"/>
@@ -23833,7 +23837,7 @@
       <c r="M120" s="39"/>
       <c r="N120" s="39"/>
     </row>
-    <row r="121" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="41"/>
       <c r="B121" s="41"/>
       <c r="C121" s="41"/>
@@ -23849,7 +23853,7 @@
       <c r="M121" s="39"/>
       <c r="N121" s="39"/>
     </row>
-    <row r="122" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="41"/>
       <c r="B122" s="41"/>
       <c r="C122" s="41"/>
@@ -23865,7 +23869,7 @@
       <c r="M122" s="39"/>
       <c r="N122" s="39"/>
     </row>
-    <row r="123" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="41"/>
       <c r="B123" s="41"/>
       <c r="C123" s="41"/>
@@ -23881,7 +23885,7 @@
       <c r="M123" s="39"/>
       <c r="N123" s="39"/>
     </row>
-    <row r="124" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="41"/>
       <c r="B124" s="41"/>
       <c r="C124" s="41"/>
@@ -23897,7 +23901,7 @@
       <c r="M124" s="39"/>
       <c r="N124" s="39"/>
     </row>
-    <row r="125" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="41"/>
       <c r="B125" s="41"/>
       <c r="C125" s="41"/>
@@ -23913,7 +23917,7 @@
       <c r="M125" s="39"/>
       <c r="N125" s="39"/>
     </row>
-    <row r="126" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
       <c r="C126" s="41"/>
@@ -23929,7 +23933,7 @@
       <c r="M126" s="39"/>
       <c r="N126" s="39"/>
     </row>
-    <row r="127" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="41"/>
       <c r="B127" s="41"/>
       <c r="C127" s="41"/>
@@ -23945,7 +23949,7 @@
       <c r="M127" s="39"/>
       <c r="N127" s="39"/>
     </row>
-    <row r="128" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="41"/>
       <c r="B128" s="41"/>
       <c r="C128" s="41"/>
@@ -23961,7 +23965,7 @@
       <c r="M128" s="39"/>
       <c r="N128" s="39"/>
     </row>
-    <row r="129" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="41"/>
       <c r="B129" s="41"/>
       <c r="C129" s="41"/>
@@ -23977,7 +23981,7 @@
       <c r="M129" s="39"/>
       <c r="N129" s="39"/>
     </row>
-    <row r="130" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="41"/>
       <c r="B130" s="41"/>
       <c r="C130" s="41"/>
@@ -23993,7 +23997,7 @@
       <c r="M130" s="39"/>
       <c r="N130" s="39"/>
     </row>
-    <row r="131" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="41"/>
       <c r="B131" s="41"/>
       <c r="C131" s="41"/>
@@ -24009,7 +24013,7 @@
       <c r="M131" s="39"/>
       <c r="N131" s="39"/>
     </row>
-    <row r="132" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="41"/>
       <c r="B132" s="41"/>
       <c r="C132" s="41"/>
@@ -24025,7 +24029,7 @@
       <c r="M132" s="39"/>
       <c r="N132" s="39"/>
     </row>
-    <row r="133" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="41"/>
       <c r="B133" s="41"/>
       <c r="C133" s="41"/>
@@ -24041,7 +24045,7 @@
       <c r="M133" s="39"/>
       <c r="N133" s="39"/>
     </row>
-    <row r="134" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="41"/>
       <c r="B134" s="41"/>
       <c r="C134" s="41"/>
@@ -24057,7 +24061,7 @@
       <c r="M134" s="39"/>
       <c r="N134" s="39"/>
     </row>
-    <row r="135" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="41"/>
       <c r="B135" s="41"/>
       <c r="C135" s="41"/>
@@ -24073,7 +24077,7 @@
       <c r="M135" s="39"/>
       <c r="N135" s="39"/>
     </row>
-    <row r="136" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="41"/>
       <c r="B136" s="41"/>
       <c r="C136" s="41"/>
@@ -24089,7 +24093,7 @@
       <c r="M136" s="39"/>
       <c r="N136" s="39"/>
     </row>
-    <row r="137" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="36" t="s">
         <v>428</v>
       </c>
@@ -24097,13 +24101,13 @@
         <v>429</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="18"/>
       <c r="B138" s="7" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="18"/>
       <c r="B139" s="7" t="s">
         <v>432</v>
@@ -24125,20 +24129,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="57.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="35.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1"/>
+    <col min="5" max="5" width="57.453125" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="35.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22">
         <v>43427</v>
       </c>
@@ -24153,7 +24157,7 @@
       <c r="H1" s="70"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
@@ -24182,7 +24186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
         <v>333</v>
       </c>
@@ -24203,7 +24207,7 @@
       </c>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18">
         <v>453163</v>
       </c>
@@ -24232,7 +24236,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>442037</v>
       </c>
@@ -24261,7 +24265,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
         <v>450183</v>
       </c>
@@ -24290,7 +24294,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>450791</v>
       </c>
@@ -24319,7 +24323,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>441347</v>
       </c>
@@ -24348,7 +24352,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>445886</v>
       </c>
@@ -24377,7 +24381,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="18">
         <v>449974</v>
       </c>
@@ -24406,7 +24410,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18">
         <v>450434</v>
       </c>
@@ -24435,7 +24439,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="18">
         <v>450050</v>
       </c>
@@ -24464,7 +24468,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18">
         <v>450620</v>
       </c>
@@ -24493,7 +24497,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
         <v>449706</v>
       </c>
@@ -24522,7 +24526,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18">
         <v>450962</v>
       </c>
@@ -24551,7 +24555,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18">
         <v>442553</v>
       </c>
@@ -24580,7 +24584,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18">
         <v>441576</v>
       </c>
@@ -24609,7 +24613,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18">
         <v>432068</v>
       </c>
@@ -24636,7 +24640,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18">
         <v>450740</v>
       </c>
@@ -24661,7 +24665,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="18">
         <v>445204</v>
       </c>
@@ -24690,7 +24694,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="18">
         <v>450955</v>
       </c>
@@ -24719,7 +24723,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="18">
         <v>450900</v>
       </c>
@@ -24746,7 +24750,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18">
         <v>442354</v>
       </c>
@@ -24773,7 +24777,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18">
         <v>450467</v>
       </c>
@@ -24800,7 +24804,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18">
         <v>449833</v>
       </c>
@@ -24829,7 +24833,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="18">
         <v>451025</v>
       </c>
@@ -24858,7 +24862,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18">
         <v>451451</v>
       </c>
@@ -24887,7 +24891,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="18">
         <v>451636</v>
       </c>
@@ -24914,7 +24918,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18">
         <v>451590</v>
       </c>
@@ -24943,7 +24947,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18">
         <v>445984</v>
       </c>
@@ -24970,7 +24974,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18">
         <v>451209</v>
       </c>
@@ -24997,7 +25001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18"/>
       <c r="B32" s="7">
         <v>43377</v>
@@ -25022,7 +25026,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="18">
         <v>449966</v>
       </c>
@@ -25049,7 +25053,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="18">
         <v>449737</v>
       </c>
@@ -25076,7 +25080,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18">
         <v>44543</v>
       </c>
@@ -25103,7 +25107,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="18">
         <v>450498</v>
       </c>
@@ -25132,7 +25136,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="18">
         <v>447204</v>
       </c>
@@ -25157,7 +25161,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18">
         <v>442108</v>
       </c>
@@ -25186,7 +25190,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18">
         <v>450377</v>
       </c>
@@ -25213,7 +25217,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="18">
         <v>432901</v>
       </c>
@@ -25240,7 +25244,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="18">
         <v>443547</v>
       </c>
@@ -25267,7 +25271,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18">
         <v>442003</v>
       </c>
@@ -25294,7 +25298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18">
         <v>445485</v>
       </c>
@@ -25321,7 +25325,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18">
         <v>442465</v>
       </c>
@@ -25348,7 +25352,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="18">
         <v>450380</v>
       </c>
@@ -25375,7 +25379,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="18">
         <v>442295</v>
       </c>
@@ -25402,7 +25406,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18">
         <v>450882</v>
       </c>
@@ -25429,7 +25433,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="18"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
@@ -25440,7 +25444,7 @@
       <c r="H48" s="9"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="18" t="s">
         <v>428</v>
       </c>
@@ -25455,7 +25459,7 @@
       <c r="H49" s="9"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="18"/>
       <c r="B50" s="7" t="s">
         <v>430</v>
@@ -25468,7 +25472,7 @@
       <c r="H50" s="9"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="18"/>
       <c r="B51" s="7" t="s">
         <v>432</v>
@@ -25481,7 +25485,7 @@
       <c r="H51" s="9"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
@@ -25492,7 +25496,7 @@
       <c r="H52" s="9"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
@@ -25503,7 +25507,7 @@
       <c r="H53" s="9"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="18"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
@@ -25514,7 +25518,7 @@
       <c r="H54" s="9"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18"/>
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
@@ -25525,7 +25529,7 @@
       <c r="H55" s="9"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="18"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
@@ -25536,7 +25540,7 @@
       <c r="H56" s="9"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
@@ -25547,7 +25551,7 @@
       <c r="H57" s="9"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="18"/>
       <c r="B58" s="7"/>
       <c r="C58" s="8"/>
@@ -25558,7 +25562,7 @@
       <c r="H58" s="9"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="18"/>
       <c r="B59" s="7"/>
       <c r="C59" s="8"/>
@@ -25569,7 +25573,7 @@
       <c r="H59" s="9"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -25580,7 +25584,7 @@
       <c r="H60" s="9"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="18"/>
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
@@ -25591,7 +25595,7 @@
       <c r="H61" s="9"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="18"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
@@ -25602,7 +25606,7 @@
       <c r="H62" s="9"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8"/>
@@ -25613,7 +25617,7 @@
       <c r="H63" s="9"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="18"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
@@ -25624,7 +25628,7 @@
       <c r="H64" s="9"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="18"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
@@ -25635,7 +25639,7 @@
       <c r="H65" s="9"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="18"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
@@ -25646,7 +25650,7 @@
       <c r="H66" s="9"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="18"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8"/>
@@ -25657,7 +25661,7 @@
       <c r="H67" s="9"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
@@ -25668,7 +25672,7 @@
       <c r="H68" s="9"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="18"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8"/>
@@ -25679,7 +25683,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="18"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -25690,7 +25694,7 @@
       <c r="H70" s="9"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="18"/>
       <c r="B71" s="7"/>
       <c r="C71" s="8"/>
@@ -25701,7 +25705,7 @@
       <c r="H71" s="9"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="18"/>
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
@@ -25712,7 +25716,7 @@
       <c r="H72" s="9"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="18"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8"/>
@@ -25723,7 +25727,7 @@
       <c r="H73" s="9"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="18"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
@@ -25734,7 +25738,7 @@
       <c r="H74" s="9"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="18"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8"/>
@@ -25745,7 +25749,7 @@
       <c r="H75" s="9"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="18"/>
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
@@ -25756,7 +25760,7 @@
       <c r="H76" s="9"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="18"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
@@ -25767,7 +25771,7 @@
       <c r="H77" s="9"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="18"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
@@ -25778,7 +25782,7 @@
       <c r="H78" s="9"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="18"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
@@ -25789,7 +25793,7 @@
       <c r="H79" s="9"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="18"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
@@ -25800,7 +25804,7 @@
       <c r="H80" s="9"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="18"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
@@ -25811,7 +25815,7 @@
       <c r="H81" s="9"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="18"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8"/>
@@ -25822,7 +25826,7 @@
       <c r="H82" s="9"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="18"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
@@ -25833,7 +25837,7 @@
       <c r="H83" s="9"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="18"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
@@ -25844,7 +25848,7 @@
       <c r="H84" s="9"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="18"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
@@ -25855,7 +25859,7 @@
       <c r="H85" s="9"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="18"/>
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
@@ -25866,7 +25870,7 @@
       <c r="H86" s="9"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="18"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
@@ -25877,7 +25881,7 @@
       <c r="H87" s="9"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="18"/>
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
@@ -25888,7 +25892,7 @@
       <c r="H88" s="9"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="18"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
@@ -25899,7 +25903,7 @@
       <c r="H89" s="9"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="18"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -25910,7 +25914,7 @@
       <c r="H90" s="9"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="18"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
@@ -25921,7 +25925,7 @@
       <c r="H91" s="9"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="18"/>
       <c r="B92" s="7"/>
       <c r="C92" s="8"/>
@@ -25932,7 +25936,7 @@
       <c r="H92" s="9"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="18"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
@@ -25943,7 +25947,7 @@
       <c r="H93" s="9"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="18"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
@@ -25954,7 +25958,7 @@
       <c r="H94" s="9"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="18"/>
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
@@ -25965,7 +25969,7 @@
       <c r="H95" s="9"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="18"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8"/>
@@ -25976,7 +25980,7 @@
       <c r="H96" s="9"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" s="2" customFormat="1" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" s="2" customFormat="1" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="19"/>
       <c r="B97" s="12"/>
       <c r="C97" s="13"/>
@@ -26003,20 +26007,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="57.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1"/>
+    <col min="5" max="5" width="57.453125" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.54296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22">
         <v>43062</v>
       </c>
@@ -26031,7 +26035,7 @@
       <c r="H1" s="70"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
@@ -26060,7 +26064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
         <v>420822</v>
       </c>
@@ -26085,7 +26089,7 @@
       <c r="H3" s="9"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18">
         <v>420998</v>
       </c>
@@ -26110,7 +26114,7 @@
       <c r="H4" s="9"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>419507</v>
       </c>
@@ -26135,7 +26139,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
         <v>424875</v>
       </c>
@@ -26160,7 +26164,7 @@
       <c r="H6" s="9"/>
       <c r="I6" s="11"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>418738</v>
       </c>
@@ -26183,7 +26187,7 @@
       <c r="H7" s="9"/>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>431855</v>
       </c>
@@ -26210,7 +26214,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>419912</v>
       </c>
@@ -26237,7 +26241,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="18">
         <v>420613</v>
       </c>
@@ -26266,7 +26270,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18">
         <v>421787</v>
       </c>
@@ -26291,7 +26295,7 @@
       <c r="H11" s="9"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="18">
         <v>420289</v>
       </c>
@@ -26320,7 +26324,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18">
         <v>421825</v>
       </c>
@@ -26345,7 +26349,7 @@
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
         <v>421664</v>
       </c>
@@ -26372,7 +26376,7 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18">
         <v>457761</v>
       </c>
@@ -26399,7 +26403,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18">
         <v>448003</v>
       </c>
@@ -26428,7 +26432,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18">
         <v>448906</v>
       </c>
@@ -26457,7 +26461,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18">
         <v>448505</v>
       </c>
@@ -26484,7 +26488,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18">
         <v>448029</v>
       </c>
@@ -26511,7 +26515,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="18">
         <v>457506</v>
       </c>
@@ -26540,7 +26544,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="18">
         <v>458887</v>
       </c>
@@ -26567,7 +26571,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="18">
         <v>423786</v>
       </c>
@@ -26596,7 +26600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18">
         <v>457452</v>
       </c>
@@ -26625,7 +26629,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18">
         <v>458234</v>
       </c>
@@ -26654,7 +26658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18">
         <v>444728</v>
       </c>
@@ -26683,7 +26687,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="18">
         <v>444640</v>
       </c>
@@ -26712,7 +26716,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18">
         <v>439546</v>
       </c>
@@ -26741,7 +26745,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="18">
         <v>439523</v>
       </c>
@@ -26770,7 +26774,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18">
         <v>444659</v>
       </c>
@@ -26799,7 +26803,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18">
         <v>439468</v>
       </c>
@@ -26826,7 +26830,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18">
         <v>439808</v>
       </c>
@@ -26855,7 +26859,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18">
         <v>439872</v>
       </c>
@@ -26882,7 +26886,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="18">
         <v>439384</v>
       </c>
@@ -26909,7 +26913,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="18" t="s">
         <v>331</v>
       </c>
@@ -26938,7 +26942,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18"/>
       <c r="B35" s="7"/>
       <c r="C35" s="8"/>
@@ -26949,7 +26953,7 @@
       <c r="H35" s="9"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="18"/>
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
@@ -26960,7 +26964,7 @@
       <c r="H36" s="9"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="18"/>
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
@@ -26971,7 +26975,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8"/>
@@ -26982,7 +26986,7 @@
       <c r="H38" s="9"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18"/>
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
@@ -26993,7 +26997,7 @@
       <c r="H39" s="9"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="18"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -27004,7 +27008,7 @@
       <c r="H40" s="9"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="18"/>
       <c r="B41" s="7"/>
       <c r="C41" s="8"/>
@@ -27015,7 +27019,7 @@
       <c r="H41" s="9"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8"/>
@@ -27026,7 +27030,7 @@
       <c r="H42" s="9"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
@@ -27037,7 +27041,7 @@
       <c r="H43" s="9"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18"/>
       <c r="B44" s="7"/>
       <c r="C44" s="8"/>
@@ -27048,7 +27052,7 @@
       <c r="H44" s="9"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="18"/>
       <c r="B45" s="7"/>
       <c r="C45" s="8"/>
@@ -27059,7 +27063,7 @@
       <c r="H45" s="9"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="18"/>
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
@@ -27070,7 +27074,7 @@
       <c r="H46" s="9"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18"/>
       <c r="B47" s="7"/>
       <c r="C47" s="8"/>
@@ -27081,7 +27085,7 @@
       <c r="H47" s="9"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="18"/>
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
@@ -27092,7 +27096,7 @@
       <c r="H48" s="9"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="18"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8"/>
@@ -27103,7 +27107,7 @@
       <c r="H49" s="9"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="18"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -27114,7 +27118,7 @@
       <c r="H50" s="9"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="18"/>
       <c r="B51" s="7"/>
       <c r="C51" s="8"/>
@@ -27125,7 +27129,7 @@
       <c r="H51" s="9"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
@@ -27136,7 +27140,7 @@
       <c r="H52" s="9"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
@@ -27147,7 +27151,7 @@
       <c r="H53" s="9"/>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="18"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
@@ -27158,7 +27162,7 @@
       <c r="H54" s="9"/>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18"/>
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
@@ -27169,7 +27173,7 @@
       <c r="H55" s="9"/>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="18"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8"/>
@@ -27180,7 +27184,7 @@
       <c r="H56" s="9"/>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
@@ -27191,7 +27195,7 @@
       <c r="H57" s="9"/>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="18"/>
       <c r="B58" s="7"/>
       <c r="C58" s="8"/>
@@ -27202,7 +27206,7 @@
       <c r="H58" s="9"/>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="18"/>
       <c r="B59" s="7"/>
       <c r="C59" s="8"/>
@@ -27213,7 +27217,7 @@
       <c r="H59" s="9"/>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -27224,7 +27228,7 @@
       <c r="H60" s="9"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="18"/>
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
@@ -27235,7 +27239,7 @@
       <c r="H61" s="9"/>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="18"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
@@ -27246,7 +27250,7 @@
       <c r="H62" s="9"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8"/>
@@ -27257,7 +27261,7 @@
       <c r="H63" s="9"/>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="18"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
@@ -27268,7 +27272,7 @@
       <c r="H64" s="9"/>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="18"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
@@ -27279,7 +27283,7 @@
       <c r="H65" s="9"/>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="18"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
@@ -27290,7 +27294,7 @@
       <c r="H66" s="9"/>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="18"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8"/>
@@ -27301,7 +27305,7 @@
       <c r="H67" s="9"/>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
@@ -27312,7 +27316,7 @@
       <c r="H68" s="9"/>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="18"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8"/>
@@ -27323,7 +27327,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="18"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -27334,7 +27338,7 @@
       <c r="H70" s="9"/>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="18"/>
       <c r="B71" s="7"/>
       <c r="C71" s="8"/>
@@ -27345,7 +27349,7 @@
       <c r="H71" s="9"/>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="18"/>
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
@@ -27356,7 +27360,7 @@
       <c r="H72" s="9"/>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="18"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8"/>
@@ -27367,7 +27371,7 @@
       <c r="H73" s="9"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="18"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
@@ -27378,7 +27382,7 @@
       <c r="H74" s="9"/>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="18"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8"/>
@@ -27389,7 +27393,7 @@
       <c r="H75" s="9"/>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="18"/>
       <c r="B76" s="7"/>
       <c r="C76" s="8"/>
@@ -27400,7 +27404,7 @@
       <c r="H76" s="9"/>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="18"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
@@ -27411,7 +27415,7 @@
       <c r="H77" s="9"/>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="18"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
@@ -27422,7 +27426,7 @@
       <c r="H78" s="9"/>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="18"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
@@ -27433,7 +27437,7 @@
       <c r="H79" s="9"/>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="18"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8"/>
@@ -27444,7 +27448,7 @@
       <c r="H80" s="9"/>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="18"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
@@ -27455,7 +27459,7 @@
       <c r="H81" s="9"/>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="18"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8"/>
@@ -27466,7 +27470,7 @@
       <c r="H82" s="9"/>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="18"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
@@ -27477,7 +27481,7 @@
       <c r="H83" s="9"/>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="18"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8"/>
@@ -27488,7 +27492,7 @@
       <c r="H84" s="9"/>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="18"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
@@ -27499,7 +27503,7 @@
       <c r="H85" s="9"/>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="18"/>
       <c r="B86" s="7"/>
       <c r="C86" s="8"/>
@@ -27510,7 +27514,7 @@
       <c r="H86" s="9"/>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="18"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
@@ -27521,7 +27525,7 @@
       <c r="H87" s="9"/>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="18"/>
       <c r="B88" s="7"/>
       <c r="C88" s="8"/>
@@ -27532,7 +27536,7 @@
       <c r="H88" s="9"/>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="18"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
@@ -27543,7 +27547,7 @@
       <c r="H89" s="9"/>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="18"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -27554,7 +27558,7 @@
       <c r="H90" s="9"/>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="18"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
@@ -27565,7 +27569,7 @@
       <c r="H91" s="9"/>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="18"/>
       <c r="B92" s="7"/>
       <c r="C92" s="8"/>
@@ -27576,7 +27580,7 @@
       <c r="H92" s="9"/>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="18"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
@@ -27587,7 +27591,7 @@
       <c r="H93" s="9"/>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="18"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
@@ -27598,7 +27602,7 @@
       <c r="H94" s="9"/>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="18"/>
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
@@ -27609,7 +27613,7 @@
       <c r="H95" s="9"/>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="18"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8"/>
@@ -27620,7 +27624,7 @@
       <c r="H96" s="9"/>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" s="2" customFormat="1" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" s="2" customFormat="1" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="19"/>
       <c r="B97" s="12"/>
       <c r="C97" s="13"/>
@@ -27647,20 +27651,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="57.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1"/>
+    <col min="5" max="5" width="57.453125" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.54296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="71" t="s">
         <v>270</v>
       </c>
@@ -27673,7 +27677,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
@@ -27702,7 +27706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
         <v>419705</v>
       </c>
@@ -27729,7 +27733,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18">
         <v>422315</v>
       </c>
@@ -27758,7 +27762,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>418802</v>
       </c>
@@ -27783,7 +27787,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
         <v>417500</v>
       </c>
@@ -27808,7 +27812,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>417007</v>
       </c>
@@ -27833,7 +27837,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>419770</v>
       </c>
@@ -27860,7 +27864,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>425060</v>
       </c>
@@ -27887,7 +27891,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="18">
         <v>417623</v>
       </c>
@@ -27912,7 +27916,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18">
         <v>419130</v>
       </c>
@@ -27937,7 +27941,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="18">
         <v>425773</v>
       </c>
@@ -27966,7 +27970,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18">
         <v>417180</v>
       </c>
@@ -27995,7 +27999,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
         <v>417729</v>
       </c>
@@ -28022,7 +28026,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18">
         <v>427865</v>
       </c>
@@ -28051,7 +28055,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18">
         <v>417029</v>
       </c>
@@ -28078,7 +28082,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18">
         <v>428586</v>
       </c>
@@ -28105,7 +28109,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18">
         <v>426139</v>
       </c>
@@ -28132,7 +28136,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18">
         <v>426400</v>
       </c>
@@ -28161,7 +28165,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="18">
         <v>421170</v>
       </c>
@@ -28190,7 +28194,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="18">
         <v>418844</v>
       </c>
@@ -28219,7 +28223,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="18">
         <v>431604</v>
       </c>
@@ -28246,7 +28250,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18">
         <v>430142</v>
       </c>
@@ -28275,7 +28279,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18">
         <v>430283</v>
       </c>
@@ -28304,7 +28308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18">
         <v>430859</v>
       </c>
@@ -28331,7 +28335,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="18">
         <v>417442</v>
       </c>
@@ -28360,7 +28364,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18">
         <v>430705</v>
       </c>
@@ -28389,7 +28393,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="18">
         <v>427393</v>
       </c>
@@ -28418,7 +28422,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18">
         <v>440261</v>
       </c>
@@ -28447,7 +28451,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18">
         <v>417512</v>
       </c>
@@ -28476,7 +28480,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="18">
         <v>430522</v>
       </c>
@@ -28505,7 +28509,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="18">
         <v>430295</v>
       </c>
@@ -28534,7 +28538,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="18">
         <v>426125</v>
       </c>
@@ -28563,7 +28567,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="18">
         <v>430464</v>
       </c>
@@ -28592,7 +28596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18">
         <v>417617</v>
       </c>
@@ -28621,7 +28625,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="18">
         <v>424951</v>
       </c>
@@ -28648,7 +28652,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="18">
         <v>417050</v>
       </c>
@@ -28677,7 +28681,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18">
         <v>440457</v>
       </c>
@@ -28706,7 +28710,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="18">
         <v>431545</v>
       </c>
@@ -28735,7 +28739,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="18">
         <v>427820</v>
       </c>
@@ -28764,7 +28768,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="18">
         <v>430868</v>
       </c>
@@ -28793,7 +28797,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18">
         <v>428167</v>
       </c>
@@ -28822,7 +28826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18">
         <v>425809</v>
       </c>
@@ -28849,7 +28853,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18">
         <v>417479</v>
       </c>
@@ -28876,7 +28880,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="18">
         <v>417955</v>
       </c>
@@ -28903,7 +28907,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="18">
         <v>433731</v>
       </c>
@@ -28930,7 +28934,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18">
         <v>428424</v>
       </c>
@@ -28957,7 +28961,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="18">
         <v>428374</v>
       </c>
@@ -28982,7 +28986,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="18">
         <v>425061</v>
       </c>
@@ -29009,7 +29013,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="18">
         <v>417451</v>
       </c>
@@ -29036,7 +29040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="18">
         <v>427727</v>
       </c>
@@ -29063,7 +29067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18">
         <v>427813</v>
       </c>
@@ -29090,7 +29094,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18">
         <v>423063</v>
       </c>
@@ -29119,7 +29123,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="18">
         <v>417464</v>
       </c>
@@ -29146,7 +29150,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18">
         <v>430078</v>
       </c>
@@ -29175,7 +29179,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="18">
         <v>417874</v>
       </c>
@@ -29202,7 +29206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18">
         <v>418175</v>
       </c>
@@ -29231,7 +29235,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="18">
         <v>425064</v>
       </c>
@@ -29258,7 +29262,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="18">
         <v>426234</v>
       </c>
@@ -29287,7 +29291,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18">
         <v>436142</v>
       </c>
@@ -29314,7 +29318,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="18">
         <v>427496</v>
       </c>
@@ -29343,7 +29347,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="18">
         <v>418828</v>
       </c>
@@ -29370,7 +29374,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18">
         <v>436331</v>
       </c>
@@ -29399,7 +29403,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="18">
         <v>428528</v>
       </c>
@@ -29426,7 +29430,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="18">
         <v>428401</v>
       </c>
@@ -29455,7 +29459,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="18">
         <v>428673</v>
       </c>
@@ -29482,7 +29486,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="18">
         <v>426195</v>
       </c>
@@ -29511,7 +29515,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18">
         <v>425765</v>
       </c>
@@ -29540,7 +29544,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="18">
         <v>417887</v>
       </c>
@@ -29569,7 +29573,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="18">
         <v>430121</v>
       </c>
@@ -29598,7 +29602,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="18">
         <v>426486</v>
       </c>
@@ -29625,7 +29629,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="18">
         <v>426633</v>
       </c>
@@ -29654,7 +29658,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="18">
         <v>418119</v>
       </c>
@@ -29677,7 +29681,7 @@
       <c r="H73" s="9"/>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="18">
         <v>433341</v>
       </c>
@@ -29706,7 +29710,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="18">
         <v>435502</v>
       </c>
@@ -29735,7 +29739,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="18">
         <v>433477</v>
       </c>
@@ -29764,7 +29768,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="18">
         <v>428420</v>
       </c>
@@ -29793,7 +29797,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="18">
         <v>426682</v>
       </c>
@@ -29818,7 +29822,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="18">
         <v>426600</v>
       </c>
@@ -29847,7 +29851,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="18">
         <v>426501</v>
       </c>
@@ -29876,7 +29880,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="18">
         <v>430067</v>
       </c>
@@ -29905,7 +29909,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="18">
         <v>422173</v>
       </c>
@@ -29934,7 +29938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="18">
         <v>437718</v>
       </c>
@@ -29961,7 +29965,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="18">
         <v>440150</v>
       </c>
@@ -29988,7 +29992,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="18">
         <v>433596</v>
       </c>
@@ -30015,7 +30019,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="18">
         <v>422812</v>
       </c>
@@ -30044,7 +30048,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="18">
         <v>426247</v>
       </c>
@@ -30073,7 +30077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="18">
         <v>435283</v>
       </c>
@@ -30100,7 +30104,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="18">
         <v>426117</v>
       </c>
@@ -30129,7 +30133,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="18">
         <v>440222</v>
       </c>
@@ -30156,7 +30160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="18">
         <v>423309</v>
       </c>
@@ -30183,7 +30187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="18">
         <v>425379</v>
       </c>
@@ -30210,7 +30214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="18">
         <v>435157</v>
       </c>
@@ -30239,7 +30243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="18">
         <v>428739</v>
       </c>
@@ -30266,7 +30270,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="18">
         <v>437873</v>
       </c>
@@ -30295,7 +30299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" s="2" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="18">
         <v>418251</v>
       </c>
@@ -30324,7 +30328,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:9" s="2" customFormat="1" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" s="2" customFormat="1" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="19">
         <v>426370</v>
       </c>
@@ -30599,15 +30603,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="aa15ca5b-4450-4fec-8212-75ae51eef6c9">
@@ -30616,6 +30611,15 @@
     <TaxCatchAll xmlns="9b77705d-b477-4602-ae15-a5316c12e631" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30638,14 +30642,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77043088-EBE2-4231-BB0C-EDD565434295}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -30654,4 +30650,12 @@
     <ds:schemaRef ds:uri="9b77705d-b477-4602-ae15-a5316c12e631"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>